--- a/コスト表 1.xlsx
+++ b/コスト表 1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirayamaMitsuha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawasaki Ryunosuke\Documents\YanRepository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D252DE98-2DA8-42D1-959B-FAC2BDB772A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B74504-10CA-41A5-ABB9-F9DF5F5298C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="埋まってるヤン編" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">埋まってるヤン編!$E$5:$F$5</definedName>
@@ -39,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
-  <si>
-    <t>1コスト:3時間 (1日は基本2コスト)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>コスト</t>
     <phoneticPr fontId="1"/>
@@ -263,13 +261,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　物理挙動</t>
-    <rPh sb="3" eb="7">
-      <t>ブツリキョドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・プレイヤー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -336,9 +327,6 @@
     <t>　ー　音量調整の処理</t>
   </si>
   <si>
-    <t>　ー　音実装</t>
-  </si>
-  <si>
     <t>・UI</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -363,9 +351,6 @@
     <t>　ー　エフェクト停止</t>
   </si>
   <si>
-    <t>　ー　座標回転と拡大</t>
-  </si>
-  <si>
     <t>　ー　エフェクト実装</t>
   </si>
   <si>
@@ -391,9 +376,6 @@
     <t>　ー　スポナー</t>
   </si>
   <si>
-    <t>　－　被弾</t>
-  </si>
-  <si>
     <t>　ー　攻撃</t>
   </si>
   <si>
@@ -431,6 +413,97 @@
   </si>
   <si>
     <t>報連相厳守！</t>
+  </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト:1時間 (1日は基本3コスト)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　－　被弾(当たり判定)</t>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　被弾(当たり判定)</t>
+    <rPh sb="3" eb="5">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>プロトタイプ</t>
+  </si>
+  <si>
+    <t>ゲームの基礎、面白さがわかる。見た目は気にしない</t>
+  </si>
+  <si>
+    <t>雑でも最後まで遊べる</t>
+  </si>
+  <si>
+    <t>ベータ</t>
+  </si>
+  <si>
+    <t>仮置きだったものを煮詰めていく。バランス調整など</t>
+  </si>
+  <si>
+    <t>マスター</t>
+  </si>
+  <si>
+    <t>主にバグ取り。仕様の追加は行わない</t>
+  </si>
+  <si>
+    <t>完全提出</t>
+  </si>
+  <si>
+    <t>9月</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10月</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -438,20 +511,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -460,7 +533,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -470,12 +543,19 @@
       <u/>
       <sz val="28"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,8 +652,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -610,15 +732,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -631,15 +744,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -649,18 +1003,16 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -679,7 +1031,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -690,6 +1042,105 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -994,119 +1445,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7FB4FF-FA90-4FC6-AD5B-A4465B00E0BA}">
-  <dimension ref="A2:N73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A2:N71"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.25" customWidth="1"/>
+    <col min="2" max="2" width="37.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.75" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
-      <c r="B2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
+      <c r="B2" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="19"/>
+        <v>71</v>
+      </c>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="B5" s="22"/>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="E5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <f>SUM(C6:C51)</f>
-        <v>0</v>
+        <f>SUM($C:$C)</f>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="17" t="b">
+      <c r="E6" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
       <c r="I6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF(E6:E49,"TRUE",C6:C49)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
         <v>5</v>
       </c>
-      <c r="J6">
-        <f>SUMIF(E6:E51,"TRUE",C6:C51)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>6</v>
-      </c>
-      <c r="N6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="17" t="b">
+      <c r="E7" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
       <c r="I7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2">
         <f ca="1">NETWORKDAYS(J8,J9)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7" s="3">
         <f ca="1" xml:space="preserve"> J6 / J7</f>
@@ -1114,7 +1565,7 @@
       </c>
       <c r="M7" s="2">
         <f ca="1">_xlfn.DAYS(J9,J8)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N7" s="3">
         <f ca="1">J6/M7</f>
@@ -1122,20 +1573,22 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="5"/>
+      <c r="B8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="I8" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" s="1">
         <f>DATE(2026,9,9)</f>
@@ -1143,137 +1596,151 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="B9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="5"/>
+      <c r="B9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="I9" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J9" s="1">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="B13" s="14" t="s">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="B14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="5"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="17" t="b">
+      <c r="E15" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="5"/>
       <c r="K15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" t="s">
         <v>21</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>22</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>23</v>
       </c>
-      <c r="N15" t="s">
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="13">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="B16" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="J16" s="1">
         <f>DATE(2026,10,20)</f>
@@ -1281,38 +1748,40 @@
       </c>
       <c r="K16" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J16)</f>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$5 - $J$6) / K16</f>
-        <v>0</v>
+        <v>3.5769230769230771</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$9)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$5 - $J$6) / M16</f>
-        <v>0</v>
+        <v>2.657142857142857</v>
       </c>
     </row>
     <row r="17" spans="2:14">
-      <c r="B17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>55</v>
+      <c r="B17" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" s="1">
         <f>DATE(2026,10,20)</f>
@@ -1320,59 +1789,63 @@
       </c>
       <c r="K17" s="2">
         <f t="shared" ref="K17:K19" ca="1" si="0">NETWORKDAYS(TODAY(),J17)</f>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L17" s="3">
         <f ca="1">($J$5 - $J$6) / K17</f>
-        <v>0</v>
+        <v>3.5769230769230771</v>
       </c>
       <c r="M17">
         <f t="shared" ref="M17:M19" ca="1" si="1">_xlfn.DAYS(J17,$J$9)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N17" s="3">
         <f ca="1">($J$5 - $J$6) / M17</f>
-        <v>0</v>
+        <v>2.657142857142857</v>
       </c>
     </row>
     <row r="18" spans="2:14">
-      <c r="B18" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>55</v>
+      <c r="B18" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="13">
+        <v>5</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="16"/>
+        <v>64</v>
+      </c>
+      <c r="I18" s="14"/>
       <c r="J18" s="1"/>
       <c r="K18" s="2"/>
       <c r="L18" s="3"/>
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="2:14">
-      <c r="B19" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>55</v>
+      <c r="B19" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="13">
+        <v>4</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>72</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J19" s="1">
         <f>DATE(2026,10,20)</f>
@@ -1380,37 +1853,39 @@
       </c>
       <c r="K19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L19" s="3">
         <f ca="1">($J$5 - $J$6) / K19</f>
-        <v>0</v>
+        <v>3.5769230769230771</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="1"/>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N19" s="3">
         <f ca="1">($J$5 - $J$6) / M19</f>
-        <v>0</v>
+        <v>2.657142857142857</v>
       </c>
     </row>
     <row r="20" spans="2:14">
-      <c r="B20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="20" t="s">
+      <c r="B20" s="13" t="s">
         <v>55</v>
       </c>
+      <c r="C20" s="13">
+        <v>10</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>51</v>
+      </c>
       <c r="G20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="15"/>
+        <v>64</v>
+      </c>
+      <c r="I20" s="13"/>
       <c r="J20" s="1"/>
       <c r="K20" s="2"/>
       <c r="L20" s="3"/>
@@ -1418,499 +1893,915 @@
     </row>
     <row r="21" spans="2:14">
       <c r="B21" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="17" t="b">
+      <c r="E21" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
-      <c r="I21" s="13"/>
+      <c r="I21" s="17"/>
       <c r="J21" s="1"/>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="2:14">
-      <c r="B22" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>55</v>
+      <c r="B22" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="13">
+        <v>5</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="2:14">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="13">
+        <v>4</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="13">
+        <v>2</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="13">
+        <v>2</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="13">
+        <v>2</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14">
-      <c r="B24" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
-      <c r="B25" s="14" t="s">
+      <c r="C27" s="13">
+        <v>4</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14">
-      <c r="B26" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="B27" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="B28" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>55</v>
+      <c r="C28" s="13">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="17" t="b">
+      <c r="E29" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="2:14">
-      <c r="B30" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>55</v>
+      <c r="B30" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="13">
+        <v>6</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="2:14">
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="13">
+        <v>6</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="32" spans="2:14">
       <c r="B32" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="17" t="b">
+      <c r="E32" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>67</v>
+      <c r="B33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="13">
+        <v>2</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>67</v>
+      <c r="B34" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="13">
+        <v>3</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="17" t="b">
+      <c r="E35" s="15" t="b">
         <v>0</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="13">
+        <v>2</v>
+      </c>
+      <c r="D36" s="13"/>
+      <c r="E36" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="13">
+        <v>5</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="21" t="s">
+      <c r="C38" s="13">
+        <v>3</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="13">
+        <v>3</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="21" t="s">
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="13">
+        <v>3</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="14" t="s">
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="4" t="s">
+      <c r="C42" s="13">
+        <v>3</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="14" t="s">
+      <c r="C44" s="13">
+        <v>3</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="14" t="s">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="14" t="s">
+      <c r="C46" s="13">
+        <v>5</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="4" t="s">
+      <c r="C47" s="13">
+        <v>5</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="14" t="s">
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49" s="5"/>
+    </row>
+    <row r="68" spans="9:9">
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="9:9">
+      <c r="I69" s="1"/>
     </row>
     <row r="70" spans="9:9">
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="9:9">
       <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="9:9">
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="9:9">
-      <c r="I73" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="E5:F5" xr:uid="{DD7FB4FF-FA90-4FC6-AD5B-A4465B00E0BA}"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G3"/>
   </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E581A4B4-A182-4031-9606-CA2BEB87BEC6}">
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="40"/>
+      <c r="B1" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29">
+        <v>2</v>
+      </c>
+      <c r="F2" s="29">
+        <v>3</v>
+      </c>
+      <c r="G2" s="29">
+        <v>4</v>
+      </c>
+      <c r="H2" s="45">
+        <v>5</v>
+      </c>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="44"/>
+      <c r="B3" s="37">
+        <v>6</v>
+      </c>
+      <c r="C3" s="37">
+        <v>7</v>
+      </c>
+      <c r="D3" s="37">
+        <v>8</v>
+      </c>
+      <c r="E3" s="37">
+        <v>9</v>
+      </c>
+      <c r="F3" s="37">
+        <v>10</v>
+      </c>
+      <c r="G3" s="37">
+        <v>11</v>
+      </c>
+      <c r="H3" s="46">
+        <v>12</v>
+      </c>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="44"/>
+      <c r="B4" s="37">
+        <v>13</v>
+      </c>
+      <c r="C4" s="37">
+        <v>14</v>
+      </c>
+      <c r="D4" s="30">
+        <v>15</v>
+      </c>
+      <c r="E4" s="30">
+        <v>16</v>
+      </c>
+      <c r="F4" s="30">
+        <v>17</v>
+      </c>
+      <c r="G4" s="30">
+        <v>18</v>
+      </c>
+      <c r="H4" s="55">
+        <v>19</v>
+      </c>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="44"/>
+      <c r="B5" s="30">
+        <v>20</v>
+      </c>
+      <c r="C5" s="30">
+        <v>21</v>
+      </c>
+      <c r="D5" s="30">
+        <v>22</v>
+      </c>
+      <c r="E5" s="30">
+        <v>23</v>
+      </c>
+      <c r="F5" s="30">
+        <v>24</v>
+      </c>
+      <c r="G5" s="30">
+        <v>25</v>
+      </c>
+      <c r="H5" s="55">
+        <v>26</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+    </row>
+    <row r="6" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A6" s="47"/>
+      <c r="B6" s="30">
+        <v>27</v>
+      </c>
+      <c r="C6" s="30">
+        <v>28</v>
+      </c>
+      <c r="D6" s="30">
+        <v>29</v>
+      </c>
+      <c r="E6" s="30">
+        <v>30</v>
+      </c>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="57">
+        <v>1</v>
+      </c>
+      <c r="G7" s="57">
+        <v>2</v>
+      </c>
+      <c r="H7" s="58">
+        <v>3</v>
+      </c>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="44"/>
+      <c r="B8" s="56">
+        <v>4</v>
+      </c>
+      <c r="C8" s="56">
+        <v>5</v>
+      </c>
+      <c r="D8" s="56">
+        <v>6</v>
+      </c>
+      <c r="E8" s="56">
+        <v>7</v>
+      </c>
+      <c r="F8" s="36">
+        <v>8</v>
+      </c>
+      <c r="G8" s="36">
+        <v>9</v>
+      </c>
+      <c r="H8" s="59">
+        <v>10</v>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="44"/>
+      <c r="B9" s="36">
+        <v>11</v>
+      </c>
+      <c r="C9" s="36">
+        <v>12</v>
+      </c>
+      <c r="D9" s="36">
+        <v>13</v>
+      </c>
+      <c r="E9" s="36">
+        <v>14</v>
+      </c>
+      <c r="F9" s="53">
+        <v>15</v>
+      </c>
+      <c r="G9" s="53">
+        <v>16</v>
+      </c>
+      <c r="H9" s="54">
+        <v>17</v>
+      </c>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="44"/>
+      <c r="B10" s="53">
+        <v>18</v>
+      </c>
+      <c r="C10" s="53">
+        <v>19</v>
+      </c>
+      <c r="D10" s="52">
+        <v>20</v>
+      </c>
+      <c r="E10" s="37">
+        <v>21</v>
+      </c>
+      <c r="F10" s="37">
+        <v>22</v>
+      </c>
+      <c r="G10" s="37">
+        <v>23</v>
+      </c>
+      <c r="H10" s="46">
+        <v>24</v>
+      </c>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+    </row>
+    <row r="11" spans="1:14" ht="19.5" thickBot="1">
+      <c r="A11" s="49"/>
+      <c r="B11" s="50">
+        <v>25</v>
+      </c>
+      <c r="C11" s="50">
+        <v>26</v>
+      </c>
+      <c r="D11" s="50">
+        <v>27</v>
+      </c>
+      <c r="E11" s="50">
+        <v>28</v>
+      </c>
+      <c r="F11" s="50">
+        <v>29</v>
+      </c>
+      <c r="G11" s="50">
+        <v>30</v>
+      </c>
+      <c r="H11" s="51">
+        <v>31</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+    </row>
+    <row r="27" spans="7:7">
+      <c r="G27" s="17"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -2145,27 +3036,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2182,23 +3072,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/コスト表 1.xlsx
+++ b/コスト表 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawasaki Ryunosuke\Documents\YanRepository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renjou\Documents\GitHub\YanRepository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B74504-10CA-41A5-ABB9-F9DF5F5298C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40743AD9-9A75-4429-8D78-3F706DE6C753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="埋まってるヤン編" sheetId="4" r:id="rId1"/>
@@ -989,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1019,7 +1019,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1040,107 +1039,107 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1465,44 +1464,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="B5" s="20"/>
-      <c r="C5" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="24" t="s">
         <v>68</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -1529,7 +1527,7 @@
       </c>
       <c r="J6">
         <f>SUMIF(E6:E49,"TRUE",C6:C49)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="s">
         <v>5</v>
@@ -1554,22 +1552,22 @@
       </c>
       <c r="J7" s="2">
         <f ca="1">NETWORKDAYS(J8,J9)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="3">
         <f ca="1" xml:space="preserve"> J6 / J7</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M7" s="2">
         <f ca="1">_xlfn.DAYS(J9,J8)</f>
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N7" s="3">
         <f ca="1">J6/M7</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1581,7 +1579,7 @@
       <c r="E8" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -1604,7 +1602,7 @@
       <c r="E9" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -1615,7 +1613,7 @@
       </c>
       <c r="J9" s="1">
         <f ca="1">TODAY()</f>
-        <v>46280</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1627,7 +1625,7 @@
       <c r="E10" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="5" t="s">
@@ -1643,7 +1641,7 @@
       <c r="E11" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="5" t="s">
@@ -1659,7 +1657,7 @@
       <c r="E12" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="5" t="s">
@@ -1675,7 +1673,7 @@
       <c r="E13" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G13" s="5" t="s">
@@ -1691,7 +1689,7 @@
       <c r="E14" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="5" t="s">
@@ -1733,7 +1731,7 @@
       <c r="E16" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G16" s="5" t="s">
@@ -1748,19 +1746,19 @@
       </c>
       <c r="K16" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J16)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$5 - $J$6) / K16</f>
-        <v>3.5769230769230771</v>
+        <v>5.4375</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$9)</f>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$5 - $J$6) / M16</f>
-        <v>2.657142857142857</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -1774,7 +1772,7 @@
       <c r="E17" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G17" s="5" t="s">
@@ -1789,19 +1787,19 @@
       </c>
       <c r="K17" s="2">
         <f t="shared" ref="K17:K19" ca="1" si="0">NETWORKDAYS(TODAY(),J17)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L17" s="3">
         <f ca="1">($J$5 - $J$6) / K17</f>
-        <v>3.5769230769230771</v>
+        <v>5.4375</v>
       </c>
       <c r="M17">
         <f t="shared" ref="M17:M19" ca="1" si="1">_xlfn.DAYS(J17,$J$9)</f>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N17" s="3">
         <f ca="1">($J$5 - $J$6) / M17</f>
-        <v>2.657142857142857</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -1815,7 +1813,7 @@
       <c r="E18" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -1838,7 +1836,7 @@
       <c r="E19" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="5" t="s">
@@ -1853,19 +1851,19 @@
       </c>
       <c r="K19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L19" s="3">
         <f ca="1">($J$5 - $J$6) / K19</f>
-        <v>3.5769230769230771</v>
+        <v>5.4375</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="N19" s="3">
         <f ca="1">($J$5 - $J$6) / M19</f>
-        <v>2.657142857142857</v>
+        <v>4.1428571428571432</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -1879,7 +1877,7 @@
       <c r="E20" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -1902,7 +1900,6 @@
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="5"/>
-      <c r="I21" s="17"/>
       <c r="J21" s="1"/>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
@@ -1919,7 +1916,7 @@
       <c r="E22" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -1937,7 +1934,7 @@
       <c r="E23" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="18" t="s">
         <v>72</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -1955,7 +1952,7 @@
       <c r="E24" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G24" s="5" t="s">
@@ -1973,7 +1970,7 @@
       <c r="E25" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G25" s="5" t="s">
@@ -1991,7 +1988,7 @@
       <c r="E26" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G26" s="5" t="s">
@@ -2009,7 +2006,7 @@
       <c r="E27" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G27" s="5" t="s">
@@ -2027,7 +2024,7 @@
       <c r="E28" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G28" s="5" t="s">
@@ -2057,7 +2054,7 @@
       <c r="E30" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G30" s="5" t="s">
@@ -2075,7 +2072,7 @@
       <c r="E31" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G31" s="5" t="s">
@@ -2105,7 +2102,7 @@
       <c r="E33" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G33" s="5" t="s">
@@ -2123,7 +2120,7 @@
       <c r="E34" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G34" s="5" t="s">
@@ -2153,7 +2150,7 @@
       <c r="E36" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F36" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G36" s="5" t="s">
@@ -2171,7 +2168,7 @@
       <c r="E37" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G37" s="5" t="s">
@@ -2189,7 +2186,7 @@
       <c r="E38" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="18" t="s">
         <v>72</v>
       </c>
       <c r="G38" s="5" t="s">
@@ -2219,7 +2216,7 @@
       <c r="E40" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G40" s="5" t="s">
@@ -2235,9 +2232,9 @@
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G41" s="5" t="s">
@@ -2255,7 +2252,7 @@
       <c r="E42" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="F42" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G42" s="5" t="s">
@@ -2283,9 +2280,9 @@
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="17" t="s">
         <v>51</v>
       </c>
       <c r="G44" s="5" t="s">
@@ -2315,7 +2312,7 @@
       <c r="E46" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G46" s="5" t="s">
@@ -2333,7 +2330,7 @@
       <c r="E47" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G47" s="5" t="s">
@@ -2349,7 +2346,7 @@
       <c r="E48" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G48" s="5" t="s">
@@ -2365,7 +2362,7 @@
       <c r="E49" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G49" s="5"/>
@@ -2395,385 +2392,382 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E581A4B4-A182-4031-9606-CA2BEB87BEC6}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="40"/>
-      <c r="B1" s="41" t="s">
+      <c r="A1" s="38"/>
+      <c r="B1" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27">
         <v>1</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="27">
         <v>2</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="27">
         <v>3</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="27">
         <v>4</v>
       </c>
-      <c r="H2" s="45">
+      <c r="H2" s="43">
         <v>5</v>
       </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="44"/>
-      <c r="B3" s="37">
+      <c r="A3" s="42"/>
+      <c r="B3" s="35">
         <v>6</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="35">
         <v>7</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="35">
         <v>8</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="35">
         <v>9</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="35">
         <v>10</v>
       </c>
-      <c r="G3" s="37">
+      <c r="G3" s="35">
         <v>11</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="44">
         <v>12</v>
       </c>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="44"/>
-      <c r="B4" s="37">
+      <c r="A4" s="42"/>
+      <c r="B4" s="35">
         <v>13</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="35">
         <v>14</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="28">
         <v>15</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="28">
         <v>16</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="28">
         <v>17</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="28">
         <v>18</v>
       </c>
-      <c r="H4" s="55">
+      <c r="H4" s="53">
         <v>19</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="44"/>
-      <c r="B5" s="30">
+      <c r="A5" s="42"/>
+      <c r="B5" s="28">
         <v>20</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>21</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="28">
         <v>22</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="28">
         <v>23</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="28">
         <v>24</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="28">
         <v>25</v>
       </c>
-      <c r="H5" s="55">
+      <c r="H5" s="53">
         <v>26</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
     </row>
     <row r="6" spans="1:14" ht="19.5" thickBot="1">
-      <c r="A6" s="47"/>
-      <c r="B6" s="30">
+      <c r="A6" s="45"/>
+      <c r="B6" s="28">
         <v>27</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="28">
         <v>28</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="28">
         <v>29</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="28">
         <v>30</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="27" t="s">
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27" t="s">
+      <c r="M6" s="25"/>
+      <c r="N6" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="57">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="55">
         <v>1</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="55">
         <v>2</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="56">
         <v>3</v>
       </c>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="27" t="s">
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27" t="s">
+      <c r="M7" s="25"/>
+      <c r="N7" s="25" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="44"/>
-      <c r="B8" s="56">
+      <c r="A8" s="42"/>
+      <c r="B8" s="54">
         <v>4</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="54">
         <v>5</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="54">
         <v>6</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="54">
         <v>7</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="34">
         <v>8</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="34">
         <v>9</v>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="57">
         <v>10</v>
       </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="27" t="s">
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27" t="s">
+      <c r="M8" s="25"/>
+      <c r="N8" s="25" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="44"/>
-      <c r="B9" s="36">
+      <c r="A9" s="42"/>
+      <c r="B9" s="34">
         <v>11</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="34">
         <v>12</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="34">
         <v>13</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="34">
         <v>14</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="51">
         <v>15</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="51">
         <v>16</v>
       </c>
-      <c r="H9" s="54">
+      <c r="H9" s="52">
         <v>17</v>
       </c>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="27" t="s">
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27" t="s">
+      <c r="M9" s="25"/>
+      <c r="N9" s="25" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="44"/>
-      <c r="B10" s="53">
+      <c r="A10" s="42"/>
+      <c r="B10" s="51">
         <v>18</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="51">
         <v>19</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="50">
         <v>20</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="35">
         <v>21</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="35">
         <v>22</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="35">
         <v>23</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="44">
         <v>24</v>
       </c>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="27" t="s">
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" ht="19.5" thickBot="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48">
         <v>25</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="48">
         <v>26</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="48">
         <v>27</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="48">
         <v>28</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="48">
         <v>29</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="48">
         <v>30</v>
       </c>
-      <c r="H11" s="51">
+      <c r="H11" s="49">
         <v>31</v>
       </c>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-    </row>
-    <row r="27" spans="7:7">
-      <c r="G27" s="17"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2782,26 +2776,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -3036,10 +3010,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3056,20 +3061,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/コスト表 1.xlsx
+++ b/コスト表 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\renjou\Documents\GitHub\YanRepository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HirayamaMitsuha\Documents\GitHub\YanRepository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40743AD9-9A75-4429-8D78-3F706DE6C753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D836AA0-F09A-4885-B7FB-9370848FE65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="1335" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="埋まってるヤン編" sheetId="4" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1552,22 +1550,22 @@
       </c>
       <c r="J7" s="2">
         <f ca="1">NETWORKDAYS(J8,J9)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="3">
         <f ca="1" xml:space="preserve"> J6 / J7</f>
-        <v>0.4</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="M7" s="2">
         <f ca="1">_xlfn.DAYS(J9,J8)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N7" s="3">
         <f ca="1">J6/M7</f>
-        <v>0.3</v>
+        <v>0.27272727272727271</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1613,7 +1611,7 @@
       </c>
       <c r="J9" s="1">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1746,19 +1744,19 @@
       </c>
       <c r="K16" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J16)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$5 - $J$6) / K16</f>
-        <v>5.4375</v>
+        <v>6.2142857142857144</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$9)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$5 - $J$6) / M16</f>
-        <v>4.1428571428571432</v>
+        <v>4.5789473684210522</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -1787,19 +1785,19 @@
       </c>
       <c r="K17" s="2">
         <f t="shared" ref="K17:K19" ca="1" si="0">NETWORKDAYS(TODAY(),J17)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L17" s="3">
         <f ca="1">($J$5 - $J$6) / K17</f>
-        <v>5.4375</v>
+        <v>6.2142857142857144</v>
       </c>
       <c r="M17">
         <f t="shared" ref="M17:M19" ca="1" si="1">_xlfn.DAYS(J17,$J$9)</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N17" s="3">
         <f ca="1">($J$5 - $J$6) / M17</f>
-        <v>4.1428571428571432</v>
+        <v>4.5789473684210522</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -1851,19 +1849,19 @@
       </c>
       <c r="K19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L19" s="3">
         <f ca="1">($J$5 - $J$6) / K19</f>
-        <v>5.4375</v>
+        <v>6.2142857142857144</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="1"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N19" s="3">
         <f ca="1">($J$5 - $J$6) / M19</f>
-        <v>4.1428571428571432</v>
+        <v>4.5789473684210522</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -2776,6 +2774,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -3010,27 +3028,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3047,23 +3064,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>